--- a/reports/一级子公司A_利润表_2026-11.xlsx
+++ b/reports/一级子公司A_利润表_2026-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>171150403</v>
+        <v>174843367</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166772278</v>
+        <v>166660591</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1887292482</v>
+        <v>1886729393</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>680337</v>
+        <v>682218</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7795451</v>
+        <v>7802789</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>588163</v>
+        <v>590936</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6762063</v>
+        <v>6770837</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>499238</v>
+        <v>499746</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5732409</v>
+        <v>5737617</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>460660</v>
+        <v>458776</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5274484</v>
+        <v>5277380</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>249731</v>
+        <v>248853</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2865540</v>
+        <v>2867050</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199354</v>
+        <v>198836</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2292412</v>
+        <v>2292637</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>168472920</v>
+        <v>172164002</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164094795</v>
+        <v>163981226</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84405582</v>
+        <v>84001042</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>926645103</v>
+        <v>925920084</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1547330</v>
+        <v>1544981</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>17768920</v>
+        <v>17749548</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1401923</v>
+        <v>1400179</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>16053591</v>
+        <v>16035809</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75066429</v>
+        <v>75337748</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>876955737</v>
+        <v>877086302</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1591444</v>
+        <v>1607137</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>18334764</v>
+        <v>18347210</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>699423</v>
+        <v>703060</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8026349</v>
+        <v>8028675</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2509522</v>
+        <v>2508242</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>28669490</v>
+        <v>28688641</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1097955</v>
+        <v>1103183</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>12607448</v>
+        <v>12622672</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4286811</v>
+        <v>4305403</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>49289441</v>
+        <v>49346783</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>91314</v>
+        <v>92685</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1026671</v>
+        <v>1020739</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2272358</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>26154324</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1512330</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>17429257</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>114164969</v>
+        <v>121923963</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>102011384</v>
+        <v>101570990</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>99918617</v>
+        <v>99479072</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1164806039</v>
+        <v>1163971398</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2092767</v>
+        <v>2091918</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>24069583</v>
+        <v>24049121</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3794162</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>43519265</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1216806</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>13929255</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>761966</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>8708906</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>915554</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>10455210</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>686984</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>7844781</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>457780</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5231695</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>380988</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4360672</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1748008</v>
+        <v>1751069</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>20064750</v>
+        <v>20082696</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1352667</v>
+        <v>1347887</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>15479746</v>
+        <v>15490024</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1098252</v>
+        <v>1096131</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>12607670</v>
+        <v>12617943</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8271771</v>
+        <v>8257072</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>95136708</v>
+        <v>95169123</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>354838</v>
+        <v>347889</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3993264</v>
+        <v>4011516</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>680716</v>
+        <v>686572</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>7638660</v>
+        <v>7585272</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>768656</v>
+        <v>686572</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>8661735</v>
+        <v>7585272</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>91043</v>
+        <v>92457</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1026408</v>
+        <v>1018513</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>352140</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3870731</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>665627</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>7617873</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>235711</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2582319</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176996</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1937676</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>295094</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3230962</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>953586</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>10899772</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>157073</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1724128</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117572</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1293086</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>195521</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2154691</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136585</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1507725</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97411</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1076438</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>77871</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>860734</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58414</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>645285</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>54307951</v>
+        <v>52603304</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62914825</v>
+        <v>58817400</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>379640</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4352115</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>98057</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1075564</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>151793</v>
+        <v>155100</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1710180</v>
+        <v>1698985</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>54156158</v>
+        <v>52827844</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5376119</v>
+        <v>5487587</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>60418986</v>
+        <v>60087717</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48780039</v>
+        <v>47340257</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48780039</v>
+        <v>47340257</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48780039</v>
+        <v>47340257</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48780039</v>
+        <v>47340257</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48780039</v>
+        <v>47340257</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
